--- a/buildplan_generator/output/25-096 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-096 GENERATED BUILD PLAN.xlsx
@@ -74,12 +74,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4EC"/>
-        <bgColor rgb="00FCE4EC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
       </patternFill>
@@ -88,6 +82,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
         <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4EC"/>
+        <bgColor rgb="00FCE4EC"/>
       </patternFill>
     </fill>
   </fills>
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-097, 25-036, 25-034, 23-061, 23-035</t>
+          <t>25-097, 25-111, 23-060, 25-109, 25-113</t>
         </is>
       </c>
     </row>
@@ -635,17 +635,15 @@
         </is>
       </c>
       <c r="E6" s="8" t="n"/>
-      <c r="F6" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-1.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I6" s="8" t="n"/>
@@ -673,12 +671,12 @@
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I7" s="8" t="n"/>
@@ -722,8 +720,8 @@
       <c r="E9" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F9" s="10" t="n">
-        <v>2</v>
+      <c r="F9" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -732,7 +730,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>1.0-3.5</t>
+          <t>ratio=0.75 (0.50-0.88)</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -759,8 +757,8 @@
       <c r="E10" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F10" s="10" t="n">
-        <v>5</v>
+      <c r="F10" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -769,7 +767,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>3.5-14.0</t>
+          <t>ratio=0.50 (0.50-0.86)</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -813,8 +811,8 @@
       <c r="E12" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F12" s="10" t="n">
-        <v>6</v>
+      <c r="F12" s="9" t="n">
+        <v>7</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
@@ -823,7 +821,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>5.0-10.5</t>
+          <t>ratio=0.88 (0.40-0.90)</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
@@ -850,7 +848,7 @@
       <c r="E13" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F13" s="10" t="n">
+      <c r="F13" s="9" t="n">
         <v>4</v>
       </c>
       <c r="G13" s="8" t="inlineStr">
@@ -860,7 +858,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>2.5-6.5</t>
+          <t>ratio=1.00 (0.38-1.20)</t>
         </is>
       </c>
       <c r="I13" s="8" t="n"/>
@@ -905,16 +903,16 @@
         <v>10</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>3.0-5.5</t>
+          <t>ratio=0.70 (n=2)</t>
         </is>
       </c>
       <c r="I15" s="8" t="n"/>
@@ -963,12 +961,12 @@
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>ratio=1.00 (n=2)</t>
         </is>
       </c>
       <c r="I17" s="8" t="n"/>
@@ -1012,7 +1010,7 @@
       <c r="E19" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="11" t="n">
+      <c r="F19" s="10" t="n">
         <v>1</v>
       </c>
       <c r="G19" s="8" t="inlineStr">
@@ -1022,7 +1020,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>ratio=1.00 (n=1)</t>
         </is>
       </c>
       <c r="I19" s="8" t="n"/>
@@ -1050,12 +1048,12 @@
       <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I20" s="8" t="n"/>
@@ -1082,8 +1080,8 @@
       <c r="E21" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F21" s="10" t="n">
-        <v>5</v>
+      <c r="F21" s="9" t="n">
+        <v>4.8</v>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
@@ -1092,7 +1090,7 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>4.5-5.0</t>
+          <t>ratio=1.21 (1.12-1.50)</t>
         </is>
       </c>
       <c r="I21" s="8" t="n"/>
@@ -1119,7 +1117,7 @@
       <c r="E22" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F22" s="10" t="n">
+      <c r="F22" s="9" t="n">
         <v>3.8</v>
       </c>
       <c r="G22" s="8" t="inlineStr">
@@ -1129,7 +1127,7 @@
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>3.5-4.0</t>
+          <t>ratio=0.94 (0.75-1.50)</t>
         </is>
       </c>
       <c r="I22" s="8" t="n"/>
@@ -1171,17 +1169,15 @@
         </is>
       </c>
       <c r="E24" s="8" t="n"/>
-      <c r="F24" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-2.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I24" s="8" t="n"/>
@@ -1209,16 +1205,16 @@
         <v>3</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>1.0-3.0</t>
+          <t>ratio=1.00 (n=2)</t>
         </is>
       </c>
       <c r="I25" s="8" t="n"/>
@@ -1246,16 +1242,16 @@
         <v>3</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>2.0-3.0</t>
+          <t>ratio=0.83 (n=2)</t>
         </is>
       </c>
       <c r="I26" s="8" t="n"/>
@@ -1283,16 +1279,16 @@
         <v>6</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>3.0-4.0</t>
+          <t>ratio=0.92 (n=2)</t>
         </is>
       </c>
       <c r="I27" s="8" t="n"/>
@@ -1336,7 +1332,7 @@
       <c r="E29" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F29" s="11" t="n">
+      <c r="F29" s="10" t="n">
         <v>1</v>
       </c>
       <c r="G29" s="8" t="inlineStr">
@@ -1346,7 +1342,7 @@
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>0.5-1.5</t>
+          <t>ratio=1.00 (n=1)</t>
         </is>
       </c>
       <c r="I29" s="8" t="n"/>
@@ -1373,7 +1369,7 @@
       <c r="E30" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F30" s="11" t="n">
+      <c r="F30" s="10" t="n">
         <v>1</v>
       </c>
       <c r="G30" s="8" t="inlineStr">
@@ -1383,7 +1379,7 @@
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>ratio=1.00 (n=1)</t>
         </is>
       </c>
       <c r="I30" s="8" t="n"/>
@@ -1410,8 +1406,8 @@
       <c r="E31" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F31" s="11" t="n">
-        <v>1</v>
+      <c r="F31" s="10" t="n">
+        <v>0.5</v>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
@@ -1420,7 +1416,7 @@
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>ratio=0.50 (n=1)</t>
         </is>
       </c>
       <c r="I31" s="8" t="n"/>
@@ -1465,12 +1461,12 @@
       <c r="F33" s="8" t="n"/>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I33" s="8" t="n"/>
@@ -1498,16 +1494,16 @@
         <v>4</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>1.5-8.5</t>
+          <t>ratio=0.88 (n=2)</t>
         </is>
       </c>
       <c r="I34" s="8" t="n"/>
@@ -1532,17 +1528,15 @@
         </is>
       </c>
       <c r="E35" s="8" t="n"/>
-      <c r="F35" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="F35" s="8" t="n"/>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-1.5</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -1570,16 +1564,16 @@
         <v>4</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>1.5-4.0</t>
+          <t>ratio=2.00 (n=2)</t>
         </is>
       </c>
       <c r="I36" s="8" t="n"/>
@@ -1607,16 +1601,16 @@
         <v>1</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=2.00 (n=1)</t>
         </is>
       </c>
       <c r="I37" s="8" t="n"/>
@@ -1661,16 +1655,16 @@
         <v>14</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>4.0-8.0</t>
+          <t>ratio=0.79 (n=2)</t>
         </is>
       </c>
       <c r="I39" s="8" t="n"/>
@@ -1698,16 +1692,16 @@
         <v>1</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>0.5-1.5</t>
+          <t>ratio=1.50 (n=1)</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -1752,16 +1746,16 @@
         <v>1</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>0.5-0.5</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="I42" s="8" t="n"/>
@@ -1786,17 +1780,15 @@
         </is>
       </c>
       <c r="E43" s="8" t="n"/>
-      <c r="F43" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="F43" s="8" t="n"/>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>global:1.5-4.5</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I43" s="8" t="n"/>
@@ -1824,12 +1816,12 @@
       <c r="F44" s="8" t="n"/>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I44" s="8" t="n"/>
@@ -1874,16 +1866,16 @@
         <v>1</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>0.5-3.5</t>
+          <t>ratio=2.25 (n=2)</t>
         </is>
       </c>
       <c r="I46" s="8" t="n"/>
@@ -1911,16 +1903,16 @@
         <v>5</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>5.0-10.8</t>
+          <t>ratio=1.51 (n=2)</t>
         </is>
       </c>
       <c r="I47" s="8" t="n"/>
@@ -1948,12 +1940,12 @@
       <c r="F48" s="8" t="n"/>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I48" s="8" t="n"/>
@@ -1981,12 +1973,12 @@
       <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I49" s="8" t="n"/>
@@ -2014,16 +2006,16 @@
         <v>5</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>6</v>
+        <v>3.8</v>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>1.5-7.0</t>
+          <t>ratio=0.76 (n=2)</t>
         </is>
       </c>
       <c r="I50" s="8" t="n"/>
@@ -2051,12 +2043,12 @@
       <c r="F51" s="8" t="n"/>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I51" s="8" t="n"/>
@@ -2101,16 +2093,16 @@
         <v>1</v>
       </c>
       <c r="F53" s="10" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>1.5-8.0</t>
+          <t>ratio=3.50 (n=2)</t>
         </is>
       </c>
       <c r="I53" s="8" t="n"/>
@@ -2138,12 +2130,12 @@
       <c r="F54" s="8" t="n"/>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I54" s="8" t="n"/>
@@ -2171,16 +2163,16 @@
         <v>1</v>
       </c>
       <c r="F55" s="10" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>2.0-4.0</t>
+          <t>ratio=2.50 (n=2)</t>
         </is>
       </c>
       <c r="I55" s="8" t="n"/>
@@ -2194,7 +2186,7 @@
         </is>
       </c>
       <c r="F57" s="1" t="n">
-        <v>83.8</v>
+        <v>95.7</v>
       </c>
     </row>
   </sheetData>
@@ -2262,7 +2254,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-097, 25-036, 25-034, 23-061, 23-035</t>
+          <t>25-097, 25-111, 23-060, 25-109, 25-113</t>
         </is>
       </c>
     </row>
@@ -3580,28 +3572,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>25-036</t>
+          <t>25-111</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>25-034</t>
+          <t>23-060</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>23-061</t>
+          <t>25-109</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>23-035</t>
+          <t>25-113</t>
         </is>
       </c>
     </row>
@@ -3656,23 +3648,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>global:1.0-1.0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3690,19 +3678,15 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>23-035, 23-061, 25-034, 25-036, 25-097</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3716,7 +3700,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3725,12 +3709,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.0-3.5</t>
+          <t>ratio=0.75 (0.50-0.88)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>25-097, 25-036, 25-034, 23-061, 23-035</t>
+          <t>25-109, 25-097, 23-060</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3730,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3755,12 +3739,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3.5-14.0</t>
+          <t>ratio=0.50 (0.50-0.86)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>25-097, 25-036, 25-034, 23-061, 23-035</t>
+          <t>25-109, 25-097, 23-060</t>
         </is>
       </c>
     </row>
@@ -3776,7 +3760,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3785,12 +3769,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>5.0-10.5</t>
+          <t>ratio=0.88 (0.40-0.90)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>25-097, 25-036, 25-034, 23-061, 23-035</t>
+          <t>25-113, 25-111, 25-109, 25-097, 23-060</t>
         </is>
       </c>
     </row>
@@ -3815,12 +3799,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2.5-6.5</t>
+          <t>ratio=1.00 (0.38-1.20)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>25-097, 25-036, 25-034</t>
+          <t>25-111, 25-109, 25-097</t>
         </is>
       </c>
     </row>
@@ -3836,21 +3820,21 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3.0-5.5</t>
+          <t>ratio=0.70 (n=2)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>25-097, 23-061, 23-035</t>
+          <t>25-097, 23-060</t>
         </is>
       </c>
     </row>
@@ -3870,17 +3854,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>ratio=1.00 (n=2)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25-097, 25-036, 25-034, 23-061, 23-035</t>
+          <t>25-097, 23-060</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3889,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>ratio=1.00 (n=1)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3930,19 +3914,15 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>23-035, 23-061, 25-034, 25-036, 25-097</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3956,7 +3936,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3965,12 +3945,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>4.5-5.0</t>
+          <t>ratio=1.21 (1.12-1.50)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>25-097, 25-036, 25-034, 23-061</t>
+          <t>25-113, 25-111, 25-097, 23-060</t>
         </is>
       </c>
     </row>
@@ -3995,12 +3975,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3.5-4.0</t>
+          <t>ratio=0.94 (0.75-1.50)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>25-097, 25-036, 25-034, 23-061</t>
+          <t>25-113, 25-111, 25-097, 23-060</t>
         </is>
       </c>
     </row>
@@ -4016,23 +3996,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>global:1.0-2.0</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4046,21 +4022,21 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.0-3.0</t>
+          <t>ratio=1.00 (n=2)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>25-097, 23-061, 23-035</t>
+          <t>25-097, 23-060</t>
         </is>
       </c>
     </row>
@@ -4076,21 +4052,21 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2.0-3.0</t>
+          <t>ratio=0.83 (n=2)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>25-097, 23-061, 23-035</t>
+          <t>25-097, 23-060</t>
         </is>
       </c>
     </row>
@@ -4106,21 +4082,21 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3.0-4.0</t>
+          <t>ratio=0.92 (n=2)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>25-097, 23-061, 23-035</t>
+          <t>25-097, 23-060</t>
         </is>
       </c>
     </row>
@@ -4136,23 +4112,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>global:1.0-2.0</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4175,12 +4147,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0.5-1.5</t>
+          <t>ratio=1.00 (n=1)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>25-097, 25-036, 23-061, 23-035</t>
+          <t>23-060</t>
         </is>
       </c>
     </row>
@@ -4205,12 +4177,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>ratio=1.00 (n=1)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>25-097, 23-061, 23-035</t>
+          <t>23-060</t>
         </is>
       </c>
     </row>
@@ -4226,7 +4198,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4235,12 +4207,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>ratio=0.50 (n=1)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>25-097, 23-061, 23-035</t>
+          <t>23-060</t>
         </is>
       </c>
     </row>
@@ -4260,19 +4232,15 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>23-035, 23-061, 25-097</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4286,21 +4254,21 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.5-8.5</t>
+          <t>ratio=0.88 (n=2)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>25-097, 25-036, 25-034, 23-061, 23-035</t>
+          <t>25-097, 23-060</t>
         </is>
       </c>
     </row>
@@ -4316,23 +4284,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>global:1.0-1.5</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4346,21 +4310,21 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.5-4.0</t>
+          <t>ratio=2.00 (n=2)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>25-097, 23-061, 23-035</t>
+          <t>25-097, 23-060</t>
         </is>
       </c>
     </row>
@@ -4376,21 +4340,21 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=2.00 (n=1)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>25-097, 25-036, 25-034, 23-061, 23-035</t>
+          <t>23-060</t>
         </is>
       </c>
     </row>
@@ -4406,21 +4370,21 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>4.0-8.0</t>
+          <t>ratio=0.79 (n=2)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>25-097, 25-034, 23-061, 23-035</t>
+          <t>25-097, 23-060</t>
         </is>
       </c>
     </row>
@@ -4436,21 +4400,21 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.5-1.5</t>
+          <t>ratio=1.50 (n=1)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>25-097, 25-036, 25-034, 23-061, 23-035</t>
+          <t>25-097</t>
         </is>
       </c>
     </row>
@@ -4466,21 +4430,21 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0.5-0.5</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>25-097, 25-036, 25-034, 23-061, 23-035</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -4496,23 +4460,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>global:1.5-4.5</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4530,19 +4490,15 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>23-035, 23-061, 25-097</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4556,21 +4512,21 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.5-3.5</t>
+          <t>ratio=2.25 (n=2)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>25-097, 25-036, 25-034, 23-061, 23-035</t>
+          <t>25-097, 23-060</t>
         </is>
       </c>
     </row>
@@ -4586,21 +4542,21 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>5.0-10.8</t>
+          <t>ratio=1.51 (n=2)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>25-097, 25-036, 25-034, 23-061, 23-035</t>
+          <t>25-097, 23-060</t>
         </is>
       </c>
     </row>
@@ -4620,19 +4576,15 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>23-035, 23-061, 25-034, 25-036, 25-097</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4650,19 +4602,15 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>23-035, 23-061, 25-097</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4676,21 +4624,21 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>6</v>
+        <v>3.8</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.5-7.0</t>
+          <t>ratio=0.76 (n=2)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>25-097, 25-036, 25-034, 23-061, 23-035</t>
+          <t>25-097, 23-060</t>
         </is>
       </c>
     </row>
@@ -4710,19 +4658,15 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>23-035, 23-061, 25-034, 25-036, 25-097</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4736,21 +4680,21 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.5-8.0</t>
+          <t>ratio=3.50 (n=2)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>25-097, 25-036, 25-034, 23-061, 23-035</t>
+          <t>25-097, 23-060</t>
         </is>
       </c>
     </row>
@@ -4770,19 +4714,15 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>23-035, 23-061, 25-034, 25-036, 25-097</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4796,21 +4736,21 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2.0-4.0</t>
+          <t>ratio=2.50 (n=2)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>25-097, 25-036, 25-034, 23-061, 23-035</t>
+          <t>25-097, 23-060</t>
         </is>
       </c>
     </row>

--- a/buildplan_generator/output/25-096 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-096 GENERATED BUILD PLAN.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-097, 25-111, 23-060, 25-109, 25-113</t>
+          <t>25-097, 23-060, 25-111, 23-061, 25-109</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
         <v>4</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.75 (0.50-0.88)</t>
+          <t>ratio=0.62 (0.50-0.88)</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -758,7 +758,7 @@
         <v>8</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.50 (0.50-0.86)</t>
+          <t>ratio=0.61 (0.50-0.86)</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -812,7 +812,7 @@
         <v>8</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.88 (0.40-0.90)</t>
+          <t>ratio=0.75 (0.40-0.88)</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
@@ -902,17 +902,17 @@
       <c r="E15" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="F15" s="10" t="n">
-        <v>7</v>
+      <c r="F15" s="9" t="n">
+        <v>11</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.70 (n=2)</t>
+          <t>ratio=1.10 (0.30-1.10)</t>
         </is>
       </c>
       <c r="I15" s="8" t="n"/>
@@ -956,17 +956,17 @@
       <c r="E17" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F17" s="10" t="n">
+      <c r="F17" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=2)</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="I17" s="8" t="n"/>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.21 (1.12-1.50)</t>
+          <t>ratio=1.21 (0.75-1.50)</t>
         </is>
       </c>
       <c r="I21" s="8" t="n"/>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.94 (0.75-1.50)</t>
+          <t>ratio=0.94 (0.75-1.00)</t>
         </is>
       </c>
       <c r="I22" s="8" t="n"/>
@@ -1204,17 +1204,17 @@
       <c r="E25" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F25" s="10" t="n">
+      <c r="F25" s="9" t="n">
         <v>3</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=2)</t>
+          <t>ratio=1.00 (0.75-1.00)</t>
         </is>
       </c>
       <c r="I25" s="8" t="n"/>
@@ -1241,17 +1241,17 @@
       <c r="E26" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F26" s="10" t="n">
-        <v>2.5</v>
+      <c r="F26" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.83 (n=2)</t>
+          <t>ratio=1.00 (0.67-2.00)</t>
         </is>
       </c>
       <c r="I26" s="8" t="n"/>
@@ -1278,17 +1278,17 @@
       <c r="E27" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F27" s="10" t="n">
-        <v>5.5</v>
+      <c r="F27" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.92 (n=2)</t>
+          <t>ratio=1.00 (0.50-1.33)</t>
         </is>
       </c>
       <c r="I27" s="8" t="n"/>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=1)</t>
+          <t>ratio=1.00 (n=2)</t>
         </is>
       </c>
       <c r="I30" s="8" t="n"/>
@@ -1493,17 +1493,17 @@
       <c r="E34" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F34" s="10" t="n">
-        <v>3.5</v>
+      <c r="F34" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.88 (n=2)</t>
+          <t>ratio=0.50 (0.50-1.25)</t>
         </is>
       </c>
       <c r="I34" s="8" t="n"/>
@@ -1563,17 +1563,17 @@
       <c r="E36" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F36" s="10" t="n">
-        <v>8</v>
+      <c r="F36" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>ratio=2.00 (n=2)</t>
+          <t>ratio=1.00 (0.67-3.00)</t>
         </is>
       </c>
       <c r="I36" s="8" t="n"/>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>ratio=2.00 (n=1)</t>
+          <t>ratio=2.00 (n=2)</t>
         </is>
       </c>
       <c r="I37" s="8" t="n"/>
@@ -1654,17 +1654,17 @@
       <c r="E39" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="F39" s="10" t="n">
-        <v>11</v>
+      <c r="F39" s="9" t="n">
+        <v>14</v>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.79 (n=2)</t>
+          <t>ratio=1.00 (0.57-1.25)</t>
         </is>
       </c>
       <c r="I39" s="8" t="n"/>
@@ -1692,7 +1692,7 @@
         <v>1</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.50 (n=1)</t>
+          <t>ratio=1.25 (n=2)</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -1865,17 +1865,17 @@
       <c r="E46" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F46" s="10" t="n">
-        <v>2.2</v>
+      <c r="F46" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>ratio=2.25 (n=2)</t>
+          <t>ratio=1.00 (0.50-3.50)</t>
         </is>
       </c>
       <c r="I46" s="8" t="n"/>
@@ -1902,17 +1902,17 @@
       <c r="E47" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F47" s="10" t="n">
-        <v>7.6</v>
+      <c r="F47" s="9" t="n">
+        <v>4.4</v>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.51 (n=2)</t>
+          <t>ratio=0.88 (0.75-2.15)</t>
         </is>
       </c>
       <c r="I47" s="8" t="n"/>
@@ -2005,17 +2005,17 @@
       <c r="E50" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F50" s="10" t="n">
-        <v>3.8</v>
+      <c r="F50" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.76 (n=2)</t>
+          <t>ratio=0.80 (0.71-1.00)</t>
         </is>
       </c>
       <c r="I50" s="8" t="n"/>
@@ -2092,17 +2092,17 @@
       <c r="E53" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F53" s="10" t="n">
-        <v>3.5</v>
+      <c r="F53" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>ratio=3.50 (n=2)</t>
+          <t>ratio=2.00 (2.00-5.00)</t>
         </is>
       </c>
       <c r="I53" s="8" t="n"/>
@@ -2162,17 +2162,17 @@
       <c r="E55" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F55" s="10" t="n">
-        <v>2.5</v>
+      <c r="F55" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>ratio=2.50 (n=2)</t>
+          <t>ratio=3.00 (2.00-4.00)</t>
         </is>
       </c>
       <c r="I55" s="8" t="n"/>
@@ -2186,7 +2186,7 @@
         </is>
       </c>
       <c r="F57" s="1" t="n">
-        <v>95.7</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-097, 25-111, 23-060, 25-109, 25-113</t>
+          <t>25-097, 23-060, 25-111, 23-061, 25-109</t>
         </is>
       </c>
     </row>
@@ -3572,28 +3572,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>25-111</t>
+          <t>23-060</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>23-060</t>
+          <t>25-111</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>25-109</t>
+          <t>23-061</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>25-113</t>
+          <t>25-109</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ratio=0.75 (0.50-0.88)</t>
+          <t>ratio=0.62 (0.50-0.88)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>25-109, 25-097, 23-060</t>
+          <t>25-109, 25-097, 23-061, 23-060</t>
         </is>
       </c>
     </row>
@@ -3730,7 +3730,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ratio=0.50 (0.50-0.86)</t>
+          <t>ratio=0.61 (0.50-0.86)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>25-109, 25-097, 23-060</t>
+          <t>25-109, 25-097, 23-061, 23-060</t>
         </is>
       </c>
     </row>
@@ -3760,7 +3760,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3769,12 +3769,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ratio=0.88 (0.40-0.90)</t>
+          <t>ratio=0.75 (0.40-0.88)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>25-113, 25-111, 25-109, 25-097, 23-060</t>
+          <t>25-111, 25-109, 25-097, 23-061, 23-060</t>
         </is>
       </c>
     </row>
@@ -3820,21 +3820,21 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ratio=0.70 (n=2)</t>
+          <t>ratio=1.10 (0.30-1.10)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>25-097, 23-060</t>
+          <t>25-097, 23-061, 23-060</t>
         </is>
       </c>
     </row>
@@ -3854,17 +3854,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=2)</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25-097, 23-060</t>
+          <t>25-097, 23-061, 23-060</t>
         </is>
       </c>
     </row>
@@ -3945,12 +3945,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ratio=1.21 (1.12-1.50)</t>
+          <t>ratio=1.21 (0.75-1.50)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>25-113, 25-111, 25-097, 23-060</t>
+          <t>25-111, 25-097, 23-061, 23-060</t>
         </is>
       </c>
     </row>
@@ -3975,12 +3975,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ratio=0.94 (0.75-1.50)</t>
+          <t>ratio=0.94 (0.75-1.00)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>25-113, 25-111, 25-097, 23-060</t>
+          <t>25-111, 25-097, 23-061, 23-060</t>
         </is>
       </c>
     </row>
@@ -4026,17 +4026,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=2)</t>
+          <t>ratio=1.00 (0.75-1.00)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>25-097, 23-060</t>
+          <t>25-097, 23-061, 23-060</t>
         </is>
       </c>
     </row>
@@ -4052,21 +4052,21 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ratio=0.83 (n=2)</t>
+          <t>ratio=1.00 (0.67-2.00)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>25-097, 23-060</t>
+          <t>25-097, 23-061, 23-060</t>
         </is>
       </c>
     </row>
@@ -4082,21 +4082,21 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ratio=0.92 (n=2)</t>
+          <t>ratio=1.00 (0.50-1.33)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>25-097, 23-060</t>
+          <t>25-097, 23-061, 23-060</t>
         </is>
       </c>
     </row>
@@ -4177,12 +4177,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=1)</t>
+          <t>ratio=1.00 (n=2)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>23-060</t>
+          <t>23-061, 23-060</t>
         </is>
       </c>
     </row>
@@ -4254,21 +4254,21 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ratio=0.88 (n=2)</t>
+          <t>ratio=0.50 (0.50-1.25)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>25-097, 23-060</t>
+          <t>25-097, 23-061, 23-060</t>
         </is>
       </c>
     </row>
@@ -4310,21 +4310,21 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ratio=2.00 (n=2)</t>
+          <t>ratio=1.00 (0.67-3.00)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>25-097, 23-060</t>
+          <t>25-097, 23-061, 23-060</t>
         </is>
       </c>
     </row>
@@ -4349,12 +4349,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ratio=2.00 (n=1)</t>
+          <t>ratio=2.00 (n=2)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>23-060</t>
+          <t>23-061, 23-060</t>
         </is>
       </c>
     </row>
@@ -4370,21 +4370,21 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ratio=0.79 (n=2)</t>
+          <t>ratio=1.00 (0.57-1.25)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>25-097, 23-060</t>
+          <t>25-097, 23-061, 23-060</t>
         </is>
       </c>
     </row>
@@ -4400,7 +4400,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4409,12 +4409,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ratio=1.50 (n=1)</t>
+          <t>ratio=1.25 (n=2)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>25-097</t>
+          <t>25-097, 23-061</t>
         </is>
       </c>
     </row>
@@ -4512,21 +4512,21 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ratio=2.25 (n=2)</t>
+          <t>ratio=1.00 (0.50-3.50)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>25-097, 23-060</t>
+          <t>25-097, 23-061, 23-060</t>
         </is>
       </c>
     </row>
@@ -4542,21 +4542,21 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>7.6</v>
+        <v>4.4</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ratio=1.51 (n=2)</t>
+          <t>ratio=0.88 (0.75-2.15)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>25-097, 23-060</t>
+          <t>25-097, 23-061, 23-060</t>
         </is>
       </c>
     </row>
@@ -4624,21 +4624,21 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ratio=0.76 (n=2)</t>
+          <t>ratio=0.80 (0.71-1.00)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>25-097, 23-060</t>
+          <t>25-097, 23-061, 23-060</t>
         </is>
       </c>
     </row>
@@ -4680,21 +4680,21 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ratio=3.50 (n=2)</t>
+          <t>ratio=2.00 (2.00-5.00)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>25-097, 23-060</t>
+          <t>25-097, 23-061, 23-060</t>
         </is>
       </c>
     </row>
@@ -4736,21 +4736,21 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ratio=2.50 (n=2)</t>
+          <t>ratio=3.00 (2.00-4.00)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>25-097, 23-060</t>
+          <t>25-097, 23-061, 23-060</t>
         </is>
       </c>
     </row>

--- a/buildplan_generator/output/25-096 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-096 GENERATED BUILD PLAN.xlsx
@@ -53,7 +53,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -76,12 +76,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -109,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -123,7 +117,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -543,7 +536,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-097, 23-060, 25-111, 23-061, 25-109</t>
+          <t>25-097, 25-111, 23-060, 25-109, 25-113</t>
         </is>
       </c>
     </row>
@@ -638,12 +631,12 @@
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I6" s="8" t="n"/>
@@ -671,12 +664,12 @@
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I7" s="8" t="n"/>
@@ -721,7 +714,7 @@
         <v>4</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -730,7 +723,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.62 (0.50-0.88)</t>
+          <t>group_total:12h</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -758,7 +751,7 @@
         <v>8</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>4.9</v>
+        <v>7.9</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -767,7 +760,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.61 (0.50-0.86)</t>
+          <t>group_total:12h</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -812,7 +805,7 @@
         <v>8</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
@@ -821,7 +814,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.75 (0.40-0.88)</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
@@ -849,7 +842,7 @@
         <v>4</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
@@ -858,7 +851,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.38-1.20)</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="I13" s="8" t="n"/>
@@ -903,7 +896,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>11</v>
+        <v>3.5</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
@@ -912,7 +905,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.10 (0.30-1.10)</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="I15" s="8" t="n"/>
@@ -957,7 +950,7 @@
         <v>1</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>1</v>
+        <v>4.1</v>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
@@ -966,7 +959,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="I17" s="8" t="n"/>
@@ -1010,17 +1003,17 @@
       <c r="E19" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="10" t="n">
-        <v>1</v>
+      <c r="F19" s="9" t="n">
+        <v>0.1</v>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=1)</t>
+          <t>group_total:7h</t>
         </is>
       </c>
       <c r="I19" s="8" t="n"/>
@@ -1048,12 +1041,12 @@
       <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I20" s="8" t="n"/>
@@ -1081,7 +1074,7 @@
         <v>4</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
@@ -1090,7 +1083,7 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.21 (0.75-1.50)</t>
+          <t>group_total:7h</t>
         </is>
       </c>
       <c r="I21" s="8" t="n"/>
@@ -1118,7 +1111,7 @@
         <v>4</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
@@ -1127,7 +1120,7 @@
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.94 (0.75-1.00)</t>
+          <t>group_total:7h</t>
         </is>
       </c>
       <c r="I22" s="8" t="n"/>
@@ -1172,12 +1165,12 @@
       <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I24" s="8" t="n"/>
@@ -1205,7 +1198,7 @@
         <v>3</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
@@ -1214,7 +1207,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.75-1.00)</t>
+          <t>group_total:6h</t>
         </is>
       </c>
       <c r="I25" s="8" t="n"/>
@@ -1242,7 +1235,7 @@
         <v>3</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
@@ -1251,7 +1244,7 @@
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.67-2.00)</t>
+          <t>group_total:6h</t>
         </is>
       </c>
       <c r="I26" s="8" t="n"/>
@@ -1279,7 +1272,7 @@
         <v>6</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
@@ -1288,7 +1281,7 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-1.33)</t>
+          <t>group_total:6h</t>
         </is>
       </c>
       <c r="I27" s="8" t="n"/>
@@ -1332,17 +1325,17 @@
       <c r="E29" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F29" s="10" t="n">
-        <v>1</v>
+      <c r="F29" s="9" t="n">
+        <v>0.7</v>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=1)</t>
+          <t>group_total:2h</t>
         </is>
       </c>
       <c r="I29" s="8" t="n"/>
@@ -1369,17 +1362,17 @@
       <c r="E30" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F30" s="10" t="n">
-        <v>1</v>
+      <c r="F30" s="9" t="n">
+        <v>0.4</v>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=2)</t>
+          <t>group_total:2h</t>
         </is>
       </c>
       <c r="I30" s="8" t="n"/>
@@ -1406,17 +1399,17 @@
       <c r="E31" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F31" s="10" t="n">
-        <v>0.5</v>
+      <c r="F31" s="9" t="n">
+        <v>0.8</v>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.50 (n=1)</t>
+          <t>group_total:2h</t>
         </is>
       </c>
       <c r="I31" s="8" t="n"/>
@@ -1461,12 +1454,12 @@
       <c r="F33" s="8" t="n"/>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I33" s="8" t="n"/>
@@ -1494,7 +1487,7 @@
         <v>4</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>2</v>
+        <v>6.8</v>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
@@ -1503,7 +1496,7 @@
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.50 (0.50-1.25)</t>
+          <t>group_total:11h</t>
         </is>
       </c>
       <c r="I34" s="8" t="n"/>
@@ -1531,12 +1524,12 @@
       <c r="F35" s="8" t="n"/>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -1564,7 +1557,7 @@
         <v>4</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
@@ -1573,7 +1566,7 @@
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.67-3.00)</t>
+          <t>group_total:11h</t>
         </is>
       </c>
       <c r="I36" s="8" t="n"/>
@@ -1601,16 +1594,16 @@
         <v>1</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>ratio=2.00 (n=2)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I37" s="8" t="n"/>
@@ -1655,7 +1648,7 @@
         <v>14</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
@@ -1664,7 +1657,7 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.57-1.25)</t>
+          <t>group_total:17h</t>
         </is>
       </c>
       <c r="I39" s="8" t="n"/>
@@ -1691,17 +1684,17 @@
       <c r="E40" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F40" s="10" t="n">
-        <v>1.2</v>
+      <c r="F40" s="9" t="n">
+        <v>0.9</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.25 (n=2)</t>
+          <t>group_total:17h</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -1745,17 +1738,17 @@
       <c r="E42" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F42" s="11" t="n">
-        <v>1</v>
+      <c r="F42" s="9" t="n">
+        <v>1.6</v>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:17h</t>
         </is>
       </c>
       <c r="I42" s="8" t="n"/>
@@ -1783,12 +1776,12 @@
       <c r="F43" s="8" t="n"/>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I43" s="8" t="n"/>
@@ -1816,12 +1809,12 @@
       <c r="F44" s="8" t="n"/>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I44" s="8" t="n"/>
@@ -1866,7 +1859,7 @@
         <v>1</v>
       </c>
       <c r="F46" s="9" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
@@ -1875,7 +1868,7 @@
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-3.50)</t>
+          <t>group_total:27h</t>
         </is>
       </c>
       <c r="I46" s="8" t="n"/>
@@ -1903,7 +1896,7 @@
         <v>5</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
@@ -1912,7 +1905,7 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.88 (0.75-2.15)</t>
+          <t>group_total:27h</t>
         </is>
       </c>
       <c r="I47" s="8" t="n"/>
@@ -1940,12 +1933,12 @@
       <c r="F48" s="8" t="n"/>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I48" s="8" t="n"/>
@@ -1973,12 +1966,12 @@
       <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I49" s="8" t="n"/>
@@ -2006,7 +1999,7 @@
         <v>5</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>4</v>
+        <v>12.5</v>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
@@ -2015,7 +2008,7 @@
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.80 (0.71-1.00)</t>
+          <t>group_total:27h</t>
         </is>
       </c>
       <c r="I50" s="8" t="n"/>
@@ -2043,12 +2036,12 @@
       <c r="F51" s="8" t="n"/>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I51" s="8" t="n"/>
@@ -2093,7 +2086,7 @@
         <v>1</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
@@ -2102,7 +2095,7 @@
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>ratio=2.00 (2.00-5.00)</t>
+          <t>group_total:27h</t>
         </is>
       </c>
       <c r="I53" s="8" t="n"/>
@@ -2130,12 +2123,12 @@
       <c r="F54" s="8" t="n"/>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I54" s="8" t="n"/>
@@ -2172,7 +2165,7 @@
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>ratio=3.00 (2.00-4.00)</t>
+          <t>group_total:27h</t>
         </is>
       </c>
       <c r="I55" s="8" t="n"/>
@@ -2186,7 +2179,7 @@
         </is>
       </c>
       <c r="F57" s="1" t="n">
-        <v>92.09999999999999</v>
+        <v>97.8</v>
       </c>
     </row>
   </sheetData>
@@ -2254,7 +2247,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-097, 23-060, 25-111, 23-061, 25-109</t>
+          <t>25-097, 25-111, 23-060, 25-109, 25-113</t>
         </is>
       </c>
     </row>
@@ -3572,28 +3565,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>23-060</t>
+          <t>25-111</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>25-111</t>
+          <t>23-060</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>23-061</t>
+          <t>25-109</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>25-109</t>
+          <t>25-113</t>
         </is>
       </c>
     </row>
@@ -3652,15 +3645,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3678,15 +3675,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3700,7 +3701,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3709,12 +3710,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ratio=0.62 (0.50-0.88)</t>
+          <t>group_total:12h</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>25-109, 25-097, 23-061, 23-060</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -3730,7 +3731,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4.9</v>
+        <v>7.9</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3739,12 +3740,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ratio=0.61 (0.50-0.86)</t>
+          <t>group_total:12h</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>25-109, 25-097, 23-061, 23-060</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -3760,7 +3761,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3769,12 +3770,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ratio=0.75 (0.40-0.88)</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>25-111, 25-109, 25-097, 23-061, 23-060</t>
+          <t>model(CUT_PREP)</t>
         </is>
       </c>
     </row>
@@ -3790,7 +3791,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3799,12 +3800,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.38-1.20)</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>25-111, 25-109, 25-097</t>
+          <t>model(CUT_PREP)</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3821,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>11</v>
+        <v>3.5</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3829,12 +3830,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ratio=1.10 (0.30-1.10)</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>25-097, 23-061, 23-060</t>
+          <t>model(SUPPORTS)</t>
         </is>
       </c>
     </row>
@@ -3850,7 +3851,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>4.1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3859,12 +3860,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25-097, 23-061, 23-060</t>
+          <t>model(MISC_PARTS)</t>
         </is>
       </c>
     </row>
@@ -3880,21 +3881,21 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=1)</t>
+          <t>group_total:7h</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>25-097</t>
+          <t>model(SHELLS)</t>
         </is>
       </c>
     </row>
@@ -3914,15 +3915,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3936,7 +3941,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3945,12 +3950,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ratio=1.21 (0.75-1.50)</t>
+          <t>group_total:7h</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>25-111, 25-097, 23-061, 23-060</t>
+          <t>model(SHELLS)</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3971,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3975,12 +3980,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ratio=0.94 (0.75-1.00)</t>
+          <t>group_total:7h</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>25-111, 25-097, 23-061, 23-060</t>
+          <t>model(SHELLS)</t>
         </is>
       </c>
     </row>
@@ -4000,15 +4005,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4022,7 +4031,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4031,12 +4040,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.75-1.00)</t>
+          <t>group_total:6h</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>25-097, 23-061, 23-060</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -4052,7 +4061,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4061,12 +4070,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.67-2.00)</t>
+          <t>group_total:6h</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>25-097, 23-061, 23-060</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -4082,7 +4091,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4091,12 +4100,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-1.33)</t>
+          <t>group_total:6h</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>25-097, 23-061, 23-060</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -4116,15 +4125,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4138,21 +4151,21 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=1)</t>
+          <t>group_total:2h</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>23-060</t>
+          <t>model(BTM_HEAD)</t>
         </is>
       </c>
     </row>
@@ -4168,21 +4181,21 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=2)</t>
+          <t>group_total:2h</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>23-061, 23-060</t>
+          <t>model(BTM_HEAD)</t>
         </is>
       </c>
     </row>
@@ -4198,21 +4211,21 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ratio=0.50 (n=1)</t>
+          <t>group_total:2h</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>23-060</t>
+          <t>model(BTM_HEAD)</t>
         </is>
       </c>
     </row>
@@ -4232,15 +4245,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4254,7 +4271,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>6.8</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4263,12 +4280,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ratio=0.50 (0.50-1.25)</t>
+          <t>group_total:11h</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>25-097, 23-061, 23-060</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -4288,15 +4305,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4310,7 +4331,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4319,12 +4340,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.67-3.00)</t>
+          <t>group_total:11h</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>25-097, 23-061, 23-060</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -4340,21 +4361,21 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ratio=2.00 (n=2)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>23-061, 23-060</t>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -4370,7 +4391,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4379,12 +4400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.57-1.25)</t>
+          <t>group_total:17h</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>25-097, 23-061, 23-060</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -4400,21 +4421,21 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ratio=1.25 (n=2)</t>
+          <t>group_total:17h</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>25-097, 23-061</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -4430,21 +4451,21 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:17h</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -4464,15 +4485,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4490,15 +4515,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4512,7 +4541,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4521,12 +4550,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-3.50)</t>
+          <t>group_total:27h</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>25-097, 23-061, 23-060</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -4542,7 +4571,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4551,12 +4580,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ratio=0.88 (0.75-2.15)</t>
+          <t>group_total:27h</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>25-097, 23-061, 23-060</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -4576,15 +4605,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4602,15 +4635,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4624,7 +4661,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>4</v>
+        <v>12.5</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4633,12 +4670,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ratio=0.80 (0.71-1.00)</t>
+          <t>group_total:27h</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>25-097, 23-061, 23-060</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -4658,15 +4695,19 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4680,7 +4721,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4689,12 +4730,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ratio=2.00 (2.00-5.00)</t>
+          <t>group_total:27h</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>25-097, 23-061, 23-060</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -4714,15 +4755,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4745,12 +4790,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ratio=3.00 (2.00-4.00)</t>
+          <t>group_total:27h</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>25-097, 23-061, 23-060</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>

--- a/buildplan_generator/output/25-096 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-096 GENERATED BUILD PLAN.xlsx
@@ -714,7 +714,7 @@
         <v>4</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         <v>8</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>8</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>group_total:7h</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="I19" s="8" t="n"/>
@@ -1074,7 +1074,7 @@
         <v>4</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>group_total:7h</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="I21" s="8" t="n"/>
@@ -1111,7 +1111,7 @@
         <v>4</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>group_total:7h</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="I22" s="8" t="n"/>
@@ -1198,7 +1198,7 @@
         <v>3</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>3</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>6</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>1</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>group_total:2h</t>
+          <t>group_total:1h</t>
         </is>
       </c>
       <c r="I29" s="8" t="n"/>
@@ -1363,7 +1363,7 @@
         <v>1</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>group_total:2h</t>
+          <t>group_total:1h</t>
         </is>
       </c>
       <c r="I30" s="8" t="n"/>
@@ -1400,7 +1400,7 @@
         <v>1</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>group_total:2h</t>
+          <t>group_total:1h</t>
         </is>
       </c>
       <c r="I31" s="8" t="n"/>
@@ -1487,7 +1487,7 @@
         <v>4</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>group_total:11h</t>
+          <t>group_total:12h</t>
         </is>
       </c>
       <c r="I34" s="8" t="n"/>
@@ -1557,7 +1557,7 @@
         <v>4</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>group_total:11h</t>
+          <t>group_total:12h</t>
         </is>
       </c>
       <c r="I36" s="8" t="n"/>
@@ -1648,7 +1648,7 @@
         <v>14</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>14.5</v>
+        <v>13.4</v>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>group_total:17h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="I39" s="8" t="n"/>
@@ -1685,7 +1685,7 @@
         <v>1</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>group_total:17h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -1739,7 +1739,7 @@
         <v>1</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>group_total:17h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="I42" s="8" t="n"/>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>group_total:27h</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="I46" s="8" t="n"/>
@@ -1896,7 +1896,7 @@
         <v>5</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>group_total:27h</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="I47" s="8" t="n"/>
@@ -1999,7 +1999,7 @@
         <v>5</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>group_total:27h</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="I50" s="8" t="n"/>
@@ -2086,7 +2086,7 @@
         <v>1</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>group_total:27h</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="I53" s="8" t="n"/>
@@ -2156,7 +2156,7 @@
         <v>1</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>group_total:27h</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="I55" s="8" t="n"/>
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="F57" s="1" t="n">
-        <v>97.8</v>
+        <v>94.2</v>
       </c>
     </row>
   </sheetData>
@@ -3701,7 +3701,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>group_total:7h</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3941,7 +3941,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>group_total:7h</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3971,7 +3971,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>group_total:7h</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>group_total:2h</t>
+          <t>group_total:1h</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>group_total:2h</t>
+          <t>group_total:1h</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -4211,7 +4211,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>group_total:2h</t>
+          <t>group_total:1h</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>group_total:11h</t>
+          <t>group_total:12h</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>group_total:11h</t>
+          <t>group_total:12h</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4391,7 +4391,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>14.5</v>
+        <v>13.4</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>group_total:17h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>group_total:17h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4451,7 +4451,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>group_total:17h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>group_total:27h</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4571,7 +4571,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>group_total:27h</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4661,7 +4661,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>group_total:27h</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -4721,7 +4721,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>group_total:27h</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -4781,7 +4781,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>group_total:27h</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
